--- a/doc/Material/WireCreep01.xlsx
+++ b/doc/Material/WireCreep01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dd3204\Projets\spartacus\doc\Material\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEFF4B0A-AED3-4545-8C94-499698965CD6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E55F43BA-6B54-4D7B-B706-4BF804EBF2FF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bersfort-Creep" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
     <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
     <sheet name="Feuil1" sheetId="5" r:id="rId5"/>
+    <sheet name="Feuil2" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="115">
   <si>
     <t>lbs</t>
   </si>
@@ -361,6 +362,24 @@
   </si>
   <si>
     <t>d/dSig2</t>
+  </si>
+  <si>
+    <t>EpsR</t>
+  </si>
+  <si>
+    <t>SigR</t>
+  </si>
+  <si>
+    <t>E1</t>
+  </si>
+  <si>
+    <t>Sig1</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>MenegottoPinto</t>
   </si>
 </sst>
 </file>
@@ -562,7 +581,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -599,6 +618,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="19">
     <cellStyle name="Accent" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -8419,7 +8442,7 @@
         <v>0</v>
       </c>
       <c r="N61" s="1">
-        <f t="shared" ref="N61:N71" si="13">K61*I61*(M61^J61)</f>
+        <f t="shared" ref="N61:N70" si="13">K61*I61*(M61^J61)</f>
         <v>0</v>
       </c>
       <c r="Q61" s="12">
@@ -8454,11 +8477,11 @@
         <v>121800000</v>
       </c>
       <c r="D62" s="5">
-        <f t="shared" ref="D61:D71" si="19">IF(C62&lt;$B$50,0,IF(C62&lt;$B$51,$B$50,IF(C62&lt;$B$52,$B$51,IF(C62&lt;$B$53,$B$52,$B$52))))</f>
+        <f t="shared" ref="D62:D71" si="19">IF(C62&lt;$B$50,0,IF(C62&lt;$B$51,$B$50,IF(C62&lt;$B$52,$B$51,IF(C62&lt;$B$53,$B$52,$B$52))))</f>
         <v>75621314.527569532</v>
       </c>
       <c r="E62" s="1">
-        <f t="shared" ref="E61:E71" si="20">IF(C62&lt;$B$50,0,IF(C62&lt;$B$51,$E$51,IF(C62&lt;$B$52,$E$52,IF(C62&lt;$B$53,$E$53,$E$53))))</f>
+        <f t="shared" ref="E62:E71" si="20">IF(C62&lt;$B$50,0,IF(C62&lt;$B$51,$E$51,IF(C62&lt;$B$52,$E$52,IF(C62&lt;$B$53,$E$53,$E$53))))</f>
         <v>8.521707092291184E-12</v>
       </c>
       <c r="F62" s="3">
@@ -8478,7 +8501,7 @@
         <v>4.8350779377309634E-4</v>
       </c>
       <c r="J62">
-        <f t="shared" ref="J61:J71" si="21">(C62-D62)*G62+H62</f>
+        <f t="shared" ref="J62:J71" si="21">(C62-D62)*G62+H62</f>
         <v>0.16071044223689085</v>
       </c>
       <c r="K62" s="1">
@@ -10647,4 +10670,566 @@
   <pageSetup orientation="portrait" horizontalDpi="90" verticalDpi="90" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0262815-290F-4D0C-B020-032CB39692C3}">
+  <dimension ref="A1:G43"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="2" max="2" width="11.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2">
+        <v>38044206663.538246</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3">
+        <v>3765574509619.897</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4">
+        <v>-2262870239324261</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5">
+        <v>2.018639990614735E+17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8">
+        <v>59388918442.04599</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9">
+        <f>10000000</f>
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B11">
+        <f>-0.003</f>
+        <v>-3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>110</v>
+      </c>
+      <c r="B12">
+        <f>-B9</f>
+        <v>-10000000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>112</v>
+      </c>
+      <c r="B14">
+        <f>$B$5*B13^4+$B$4*B13^3+$B$3*B13^2+$B$2*B13^1+$B$1</f>
+        <v>127666615.55607696</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>111</v>
+      </c>
+      <c r="B15" s="17">
+        <f>4*$B$5*B13^3+3*$B$4*B13^2+2*$B$3*B13^1+$B$2</f>
+        <v>6916683341.1544037</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="17">
+        <f>B15/B8</f>
+        <v>0.11646420784550861</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" s="17">
+        <f>(B14-B12-B13*B15+B11*B8)/(B8-B15)</f>
+        <v>-1.4309197298621884E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>62</v>
+      </c>
+      <c r="B18">
+        <f>(B17-B11)*B8+B12</f>
+        <v>83185980.192237988</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>82</v>
+      </c>
+      <c r="B20">
+        <f>(B13-B11)/(B17-B11)</f>
+        <v>5.0985281965831888</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" t="s">
+        <v>83</v>
+      </c>
+      <c r="B21">
+        <f>B16*B20+((1-B16)*B20)/((1+B20^B19)^(1/B19))</f>
+        <v>1.477331839747533</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" t="s">
+        <v>50</v>
+      </c>
+      <c r="B22">
+        <f>B21*(B18-B12)+B12</f>
+        <v>127666615.55607611</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" t="s">
+        <v>113</v>
+      </c>
+      <c r="B23">
+        <f>ABS(B22-B14)</f>
+        <v>8.4936618804931641E-7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="1">
+        <v>-3.0000000000000001E-3</v>
+      </c>
+      <c r="B30" s="1">
+        <f>(A30-$B$13)/($B$20-$B$13)</f>
+        <v>-1.5706205386997786E-3</v>
+      </c>
+      <c r="C30" s="1" t="e">
+        <f>$B$22*B30+((1-$B$22)*B30)/((1+B30^$B$23)^(1/$B$23))</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="D30" s="1" t="e">
+        <f>C30*($B$24-$B$14)+$B$14</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="F30" s="1">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <f>$B$5*F30^4+$B$4*F30^3+$B$3*F30^2+$B$2*F30^1+$B$1</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="1">
+        <v>-2.5000000000000001E-3</v>
+      </c>
+      <c r="B31" s="1">
+        <f>(A31-$B$13)/($B$20-$B$13)</f>
+        <v>-1.4724567550310425E-3</v>
+      </c>
+      <c r="C31" s="1" t="e">
+        <f t="shared" ref="C31:C43" si="0">$B$22*B31+((1-$B$22)*B31)/((1+B31^$B$23)^(1/$B$23))</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="D31" s="1" t="e">
+        <f>C31*($B$24-$B$14)+$B$14</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="F31" s="1">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="G31">
+        <f>$B$5*F31^4+$B$4*F31^3+$B$3*F31^2+$B$2*F31^1+$B$1</f>
+        <v>19693254.679199908</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="1">
+        <v>-2E-3</v>
+      </c>
+      <c r="B32" s="1">
+        <f>(A32-$B$13)/($B$20-$B$13)</f>
+        <v>-1.3742929713623064E-3</v>
+      </c>
+      <c r="C32" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="D32" s="1" t="e">
+        <f>C32*($B$24-$B$14)+$B$14</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="F32" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="G32">
+        <f t="shared" ref="G32:G42" si="1">$B$5*F32^4+$B$4*F32^3+$B$3*F32^2+$B$2*F32^1+$B$1</f>
+        <v>39748774.932895355</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="1">
+        <v>-1.5E-3</v>
+      </c>
+      <c r="B33" s="1">
+        <f>(A33-$B$13)/($B$20-$B$13)</f>
+        <v>-1.2761291876935703E-3</v>
+      </c>
+      <c r="C33" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="D33" s="1" t="e">
+        <f>C33*($B$24-$B$14)+$B$14</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="F33" s="1">
+        <v>1.5E-3</v>
+      </c>
+      <c r="G33">
+        <f t="shared" si="1"/>
+        <v>58923602.079481468</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="1">
+        <v>-1E-3</v>
+      </c>
+      <c r="B34" s="1">
+        <f>(A34-$B$13)/($B$20-$B$13)</f>
+        <v>-1.177965404024834E-3</v>
+      </c>
+      <c r="C34" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="D34" s="1" t="e">
+        <f>C34*($B$24-$B$14)+$B$14</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="F34" s="1">
+        <v>2E-3</v>
+      </c>
+      <c r="G34">
+        <f t="shared" si="1"/>
+        <v>76277573.43594557</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="1">
+        <v>-5.0000000000000001E-4</v>
+      </c>
+      <c r="B35" s="1">
+        <f>(A35-$B$13)/($B$20-$B$13)</f>
+        <v>-1.0798016203560977E-3</v>
+      </c>
+      <c r="C35" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="D35" s="1" t="e">
+        <f>C35*($B$24-$B$14)+$B$14</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="F35" s="1">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="G35">
+        <f t="shared" si="1"/>
+        <v>91173322.317867205</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="1">
+        <v>0</v>
+      </c>
+      <c r="B36" s="1">
+        <f>(A36-$B$13)/($B$20-$B$13)</f>
+        <v>-9.8163783668736159E-4</v>
+      </c>
+      <c r="C36" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="D36" s="1" t="e">
+        <f>C36*($B$24-$B$14)+$B$14</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="F36" s="1">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="G36">
+        <f t="shared" si="1"/>
+        <v>103276278.03941813</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="1">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="B37" s="1">
+        <f>(A37-$B$13)/($B$20-$B$13)</f>
+        <v>-8.834740530186256E-4</v>
+      </c>
+      <c r="C37" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="D37" s="1" t="e">
+        <f>C37*($B$24-$B$14)+$B$14</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="F37" s="1">
+        <v>3.5000000000000001E-3</v>
+      </c>
+      <c r="G37">
+        <f t="shared" si="1"/>
+        <v>112554665.91336226</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="B38" s="1">
+        <f>(A38-$B$13)/($B$20-$B$13)</f>
+        <v>-7.8531026934988929E-4</v>
+      </c>
+      <c r="C38" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="D38" s="1" t="e">
+        <f>C38*($B$24-$B$14)+$B$14</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="F38" s="1">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="G38">
+        <f t="shared" si="1"/>
+        <v>119279507.25105587</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="1">
+        <v>1.5E-3</v>
+      </c>
+      <c r="B39" s="1">
+        <f>(A39-$B$13)/($B$20-$B$13)</f>
+        <v>-6.871464856811532E-4</v>
+      </c>
+      <c r="C39" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="D39" s="1" t="e">
+        <f>C39*($B$24-$B$14)+$B$14</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="F39" s="1">
+        <v>4.4999999999999997E-3</v>
+      </c>
+      <c r="G39">
+        <f t="shared" si="1"/>
+        <v>124024619.36244725</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="1">
+        <v>2E-3</v>
+      </c>
+      <c r="B40" s="1">
+        <f>(A40-$B$13)/($B$20-$B$13)</f>
+        <v>-5.8898270201241699E-4</v>
+      </c>
+      <c r="C40" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="D40" s="1" t="e">
+        <f>C40*($B$24-$B$14)+$B$14</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="F40" s="1">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G40">
+        <f t="shared" si="1"/>
+        <v>127666615.55607696</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="1">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="B41" s="1">
+        <f>(A41-$B$13)/($B$20-$B$13)</f>
+        <v>-4.9081891834368079E-4</v>
+      </c>
+      <c r="C41" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="D41" s="1" t="e">
+        <f>C41*($B$24-$B$14)+$B$14</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="F41" s="1">
+        <v>5.4999999999999997E-3</v>
+      </c>
+      <c r="G41">
+        <f t="shared" si="1"/>
+        <v>131384905.13907786</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="1">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="B42" s="1">
+        <f>(A42-$B$13)/($B$20-$B$13)</f>
+        <v>-3.9265513467494465E-4</v>
+      </c>
+      <c r="C42" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="D42" s="1" t="e">
+        <f>C42*($B$24-$B$14)+$B$14</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="F42" s="1">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="G42">
+        <f t="shared" si="1"/>
+        <v>136661693.41717511</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="1">
+        <v>3.5000000000000001E-3</v>
+      </c>
+      <c r="B43" s="1">
+        <f>(A43-$B$13)/($B$20-$B$13)</f>
+        <v>-2.944913510062085E-4</v>
+      </c>
+      <c r="C43" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="D43" s="1" t="e">
+        <f>C43*($B$24-$B$14)+$B$14</f>
+        <v>#NUM!</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A28:D28"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="90" verticalDpi="90" r:id="rId1"/>
+</worksheet>
 </file>